--- a/ruoyi-admin/src/main/resources/template/清洁生产列表模版.xlsx
+++ b/ruoyi-admin/src/main/resources/template/清洁生产列表模版.xlsx
@@ -7,7 +7,7 @@
     <workbookView windowWidth="22188" windowHeight="9060"/>
   </bookViews>
   <sheets>
-    <sheet name="清洁生产统计表" sheetId="1" r:id="rId1"/>
+    <sheet name="清洁生产列表" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
